--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEC2389-E9EF-4AAC-890F-16A1A031B0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0080629F-263A-4A52-ACC9-C887C34B2FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5567BFC5-6B3F-48E8-B409-21C10916E640}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B42CC9B-954E-4CA1-A0F0-AF3E4C35AD5B}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IDN_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_IDN_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IDN_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0080629F-263A-4A52-ACC9-C887C34B2FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{842A559A-1867-4CB4-B34D-5FEFE5EFC110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4646,7 +4646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B42CC9B-954E-4CA1-A0F0-AF3E4C35AD5B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1CC270C-296A-485E-AEEB-3280426811A5}">
   <dimension ref="B3:I112"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
